--- a/StructureDefinition-openimis-health-facility-organization.xlsx
+++ b/StructureDefinition-openimis-health-facility-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11025,7 +11025,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>22</v>
@@ -12675,7 +12675,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>22</v>
@@ -18162,7 +18162,7 @@
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>22</v>
@@ -18509,7 +18509,7 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>22</v>
@@ -18624,7 +18624,7 @@
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>22</v>
@@ -19092,7 +19092,7 @@
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-health-facility-organization.xlsx
+++ b/StructureDefinition-openimis-health-facility-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-health-facility-organization.xlsx
+++ b/StructureDefinition-openimis-health-facility-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
